--- a/Result/profitability/5011.xlsx
+++ b/Result/profitability/5011.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.28</v>
+        <v>-0.2575</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4325</v>
+        <v>-0.535</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>-0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2775</v>
+        <v>-0.1825</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.24125</v>
+        <v>0.7125</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1725</v>
+        <v>-0.14625</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3075</v>
+        <v>2.52125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>-0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1525</v>
+        <v>-0.09874999999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5150000000000001</v>
+        <v>1.60875</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09499999999999997</v>
+        <v>-0.04249999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5049999999999999</v>
+        <v>0.4850000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03874999999999998</v>
+        <v>1.734723475976807e-17</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1625</v>
+        <v>0.42</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01125000000000002</v>
+        <v>-0.06124999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.45625</v>
+        <v>0.4587500000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>-0.02</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.007499999999999986</v>
+        <v>-0.007499999999999989</v>
       </c>
       <c r="N11" t="n">
         <v>1.45</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5011</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D75" t="n">
+        <v>945</v>
+      </c>
+      <c r="E75" t="n">
+        <v>64</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>17</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2762499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-1.41375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.5800000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.115384615384615</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.02000000000000046</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.003174603174603163</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8775510204081632</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-3.60082304526749</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
